--- a/02_Zero_Shot/outputs/Embedding/BERT-base-uncased/RESULT_f-droid_bert-base-uncased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/BERT-base-uncased/RESULT_f-droid_bert-base-uncased_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.505872083000213</v>
+        <v>25.3414033400004</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002641982429778322</v>
+        <v>0.008919888539246884</v>
       </c>
     </row>
   </sheetData>
